--- a/backend/data/financials_by_company/1NFLX.MI.xlsx
+++ b/backend/data/financials_by_company/1NFLX.MI.xlsx
@@ -3852,212 +3852,212 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="EV1" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Wilmot Reed Hastings Jr.', 'age': 65, 'title': 'Co-Founder &amp; Chairman', 'yearBorn': 1960, 'fiscalYear': 2025, 'totalPay': 100729, 'exercisedValue': 318094432, 'unexercisedValue': 1036340288}, {'maxAge': 1, 'name': 'Mr. Theodore A. Sarandos', 'age': 60, 'title': 'Co-CEO, President &amp; Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 10751782, 'exercisedValue': 149129920, 'unexercisedValue': 257862464}, {'maxAge': 1, 'name': 'Mr. Gregory K. Peters', 'age': 54, 'title': 'Co-CEO, President &amp; Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 10134001, 'exercisedValue': 76826272, 'unexercisedValue': 122934824}, {'maxAge': 1, 'name': 'Mr. Spencer Adam Neumann', 'age': 55, 'title': 'Chief Financial Officer', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 5855427, 'exercisedValue': 21870958, 'unexercisedValue': 82518480}, {'maxAge': 1, 'name': 'Mr. David  Hyman J.D.', 'age': 59, 'title': 'Chief Legal Officer &amp; Secretary', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 5776475, 'exercisedValue': 78172384, 'unexercisedValue': 12242183}, {'maxAge': 1, 'name': 'Mr. Clete  Willems', 'age': 45, 'title': 'Chief Global Affairs Officer', 'yearBorn': 1980, 'fiscalYear': 2025, 'totalPay': 4700906, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Natalie  Gutteridge', 'title': 'VP of Corporate Legal &amp; Operations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jeffrey William Karbowski', 'age': 46, 'title': 'Chief Accounting Officer', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Elizabeth  Stone', 'title': 'Chief Product &amp; Technology Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Spencer  Wang', 'title': 'Vice President of Finance, Corporate Development &amp; Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Spencer Adam Neumann', 'age': 55, 'title': 'Chief Financial Officer', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 5938120, 'exercisedValue': 22179832, 'unexercisedValue': 83683856}, {'maxAge': 1, 'name': 'Mr. David  Hyman J.D.', 'age': 59, 'title': 'Chief Legal Officer &amp; Secretary', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 5858053, 'exercisedValue': 79276376, 'unexercisedValue': 12415075}, {'maxAge': 1, 'name': 'Mr. Clete  Willems', 'age': 45, 'title': 'Chief Global Affairs Officer', 'yearBorn': 1980, 'fiscalYear': 2025, 'totalPay': 4767295, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Natalie  Gutteridge', 'title': 'VP of Corporate Legal &amp; Operations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jeffrey William Karbowski', 'age': 46, 'title': 'Chief Accounting Officer', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Elizabeth  Stone', 'title': 'Chief Product &amp; Technology Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Spencer  Wang', 'title': 'Vice President of Finance, Corporate Development &amp; Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Dani  Dudeck', 'title': 'Chief Communications Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Marian  Lee', 'age': 45, 'title': 'Chief Marketing Officer', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bela  Bajaria', 'age': 53, 'title': 'Chief Content Officer', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4161,7 +4161,7 @@
         <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1767139200</v>
@@ -4178,64 +4178,64 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>73.70999999999999</v>
+        <v>67.87</v>
       </c>
       <c r="AB2" t="n">
-        <v>73.81999999999999</v>
+        <v>67.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>71.73</v>
+        <v>64.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>73.81999999999999</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>73.70999999999999</v>
+        <v>67.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>73.81999999999999</v>
+        <v>67.44</v>
       </c>
       <c r="AG2" t="n">
-        <v>71.73</v>
+        <v>64.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>73.81999999999999</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.548</v>
+        <v>1.491</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.928839</v>
+        <v>23.822878</v>
       </c>
       <c r="AL2" t="n">
-        <v>5648</v>
+        <v>6111</v>
       </c>
       <c r="AM2" t="n">
-        <v>5648</v>
+        <v>6111</v>
       </c>
       <c r="AN2" t="n">
-        <v>6459</v>
+        <v>6814</v>
       </c>
       <c r="AO2" t="n">
-        <v>5743</v>
+        <v>4132</v>
       </c>
       <c r="AP2" t="n">
-        <v>5743</v>
+        <v>4132</v>
       </c>
       <c r="AQ2" t="n">
-        <v>71.92</v>
+        <v>64.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>71.91</v>
+        <v>64.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>302756429824</v>
+        <v>271849144320</v>
       </c>
       <c r="AT2" t="n">
-        <v>310351004492</v>
+        <v>284370497751</v>
       </c>
       <c r="AU2" t="n">
         <v>9.548999999999999</v>
@@ -4250,13 +4250,13 @@
         <v>9.548999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.456739</v>
+        <v>5.797594</v>
       </c>
       <c r="AZ2" t="n">
-        <v>79.64700000000001</v>
+        <v>76.0534</v>
       </c>
       <c r="BA2" t="n">
-        <v>85.35593</v>
+        <v>82.88537599999999</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>307353649152</v>
+        <v>290376089600</v>
       </c>
       <c r="BG2" t="n">
         <v>0.28521</v>
@@ -4288,16 +4288,16 @@
         <v>0.00567</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.85007006</v>
+        <v>0.85103</v>
       </c>
       <c r="BL2" t="n">
         <v>4210798528</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.3435783</v>
+        <v>6.4386544</v>
       </c>
       <c r="BN2" t="n">
-        <v>11.334297</v>
+        <v>10.026939</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4315,10 +4315,10 @@
         <v>13373640704</v>
       </c>
       <c r="BT2" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -4329,16 +4329,16 @@
         <v>1763337600</v>
       </c>
       <c r="BX2" t="n">
-        <v>6.555</v>
+        <v>6.193</v>
       </c>
       <c r="BY2" t="n">
-        <v>21.511</v>
+        <v>20.322</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.3171206</v>
+        <v>-0.36994058</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>71.90000000000001</v>
+        <v>64.56</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4450,128 +4450,134 @@
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>PRE</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>-2.455566</v>
+          <t>NETFLIX</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
       </c>
       <c r="DH2" t="n">
-        <v>71.90000000000001</v>
+        <v>-3.3100052</v>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
+          <t>64.5 - 67.85</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>6814</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>55.010998</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>5.760917</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>9.549 - 114.02</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>-49.46</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.43378356</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-36.994057</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1784215800</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-18.325378</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.22109303</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>20</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>VIVEK</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>-11.493401</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.15112278</v>
+      </c>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>POSTPOST</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1782142506</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>finmb_32012</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>Europe/Rome</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
-      </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>1508828400000</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-1.8099976</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>71.73 - 73.82</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>6459</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>62.351</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>6.5295844</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>9.549 - 114.02</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>-42.119995</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.36940885</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-31.71206</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1776353400</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1784215800</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1784215800</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1776372300</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1776372300</v>
-      </c>
-      <c r="ED2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-7.7470016</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.097266704</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-13.455925</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.15764488</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>VIVEK</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EN2" t="b">
-        <v>0</v>
       </c>
       <c r="EO2" t="n">
         <v>7200000</v>
@@ -4584,26 +4590,20 @@
       <c r="EQ2" t="b">
         <v>0</v>
       </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>NETFLIX</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="ER2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>1508828400000</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-4.876978</v>
       </c>
       <c r="EU2" t="n">
-        <v>1780414514</v>
+        <v>64.56</v>
       </c>
       <c r="EV2" t="n">
-        <v>1.6864</v>
+        <v>1.5275</v>
       </c>
     </row>
   </sheetData>
